--- a/data/trans_orig/IP07A02-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07A02-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 99,4%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2007 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16268</t>
+          <t>16125</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15590</t>
+          <t>15679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24258</t>
+          <t>24102</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26419</t>
+          <t>26773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37689</t>
+          <t>38584</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11910</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26699</t>
+          <t>27358</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36133</t>
+          <t>36723</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28770</t>
+          <t>28756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40452</t>
+          <t>40636</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59165</t>
+          <t>59588</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74888</t>
+          <t>73943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>72,87%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>14742</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24264</t>
+          <t>24088</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21076</t>
+          <t>21529</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35958</t>
+          <t>36072</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6445</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25957</t>
+          <t>25222</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19129</t>
+          <t>19191</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29103</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41723</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17767</t>
+          <t>18067</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17898</t>
+          <t>17967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>20102</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32737</t>
+          <t>32901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,29%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>787</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>16628</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24097</t>
+          <t>24405</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23880</t>
+          <t>23893</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38387</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18293</t>
+          <t>18377</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28027</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12626</t>
+          <t>12389</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>22140</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32978</t>
+          <t>33917</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48167</t>
+          <t>48987</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18788</t>
+          <t>19018</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>29338</t>
+          <t>29490</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>11827</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10449</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20065</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,51%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21714</t>
+          <t>21144</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>25174</t>
+          <t>25095</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>36753</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28019</t>
+          <t>27886</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,99%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>25364</t>
+          <t>25226</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>37118</t>
+          <t>37111</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>30740</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>43118</t>
+          <t>43730</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>60313</t>
+          <t>59352</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>77200</t>
+          <t>77245</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>13985</t>
+          <t>14578</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>25448</t>
+          <t>25489</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>17428</t>
+          <t>16994</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>29568</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>34791</t>
+          <t>34208</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>52124</t>
+          <t>51312</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>43,62%</t>
         </is>
       </c>
     </row>
@@ -5050,82 +5050,82 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>1423</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>7237</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>12,92%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>3620</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
           <t>1417</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>7336</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>3620</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>1414</t>
-        </is>
-      </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>27388</t>
+          <t>27176</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>41371</t>
+          <t>41494</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>34845</t>
+          <t>35822</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>48506</t>
+          <t>49255</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>67381</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>31762</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>46420</t>
+          <t>46122</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>33150</t>
+          <t>32625</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>55337</t>
+          <t>56070</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>74385</t>
+          <t>74441</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>11453</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>145782</t>
+          <t>145351</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>174280</t>
+          <t>175179</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>174714</t>
+          <t>172278</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>203520</t>
+          <t>204023</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>328176</t>
+          <t>327218</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>369103</t>
+          <t>369716</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,58%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>122861</t>
+          <t>122966</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>151491</t>
+          <t>152239</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>121441</t>
+          <t>120362</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>150070</t>
+          <t>149107</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>254883</t>
+          <t>250931</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>295138</t>
+          <t>290826</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>13448</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>26987</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>22478</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>25661</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>44356</t>
+          <t>44750</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -6675,12 +6675,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15679</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11833</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21199</t>
+          <t>21094</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22352</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34554</t>
+          <t>34197</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,44%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15089</t>
+          <t>15414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15702</t>
+          <t>15577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27223</t>
+          <t>27675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>50,53%</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20689</t>
+          <t>20840</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31545</t>
+          <t>31813</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28015</t>
+          <t>28139</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39499</t>
+          <t>39275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52339</t>
+          <t>51566</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68212</t>
+          <t>67695</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,58%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19787</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18055</t>
+          <t>17700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20322</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34867</t>
+          <t>34765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8827</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>13634</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>9149</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18526</t>
+          <t>18424</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17478</t>
+          <t>17348</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29029</t>
+          <t>29368</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18389</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18385</t>
+          <t>19148</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>23196</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34130</t>
+          <t>34805</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>550</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>6692</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10862</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21103</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15030</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24648</t>
+          <t>24552</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29323</t>
+          <t>28145</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43659</t>
+          <t>43257</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13213</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23476</t>
+          <t>23789</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>16194</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22132</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36838</t>
+          <t>37509</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>871</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11494</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8015</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13016</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18175</t>
+          <t>17790</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16893</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23968</t>
+          <t>23358</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33722</t>
+          <t>33568</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>751</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2378</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13976</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>21071</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>16352</t>
+          <t>16682</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24745</t>
+          <t>24736</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18598</t>
+          <t>18808</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>29481</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>41204</t>
+          <t>41666</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>73,46%</t>
         </is>
       </c>
     </row>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>19433</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>17227</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>29947</t>
+          <t>28794</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>29228</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>44714</t>
+          <t>45089</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>33552</t>
+          <t>33974</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>45198</t>
+          <t>44789</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>23120</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>35519</t>
+          <t>35732</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>60369</t>
+          <t>60824</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>76982</t>
+          <t>77283</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,6%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>30128</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>43763</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>23771</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>37195</t>
+          <t>36833</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>57221</t>
+          <t>57082</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>79166</t>
+          <t>77358</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>48,61%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>30327</t>
+          <t>30586</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>44935</t>
+          <t>44550</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>37272</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>51658</t>
+          <t>52133</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>71045</t>
+          <t>70662</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>92032</t>
+          <t>91571</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>14367</t>
+          <t>14214</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -12259,7 +12259,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>108097</t>
+          <t>108446</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>136563</t>
+          <t>136731</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>135625</t>
+          <t>137516</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>165157</t>
+          <t>166651</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>255180</t>
+          <t>253635</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>296780</t>
+          <t>294191</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,07%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>157650</t>
+          <t>157122</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>187118</t>
+          <t>185586</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>136557</t>
+          <t>133764</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>166568</t>
+          <t>164726</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>298700</t>
+          <t>301737</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>343914</t>
+          <t>342502</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>17269</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>33203</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>28681</t>
+          <t>28670</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>35169</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>57138</t>
+          <t>57174</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13335</t>
+          <t>13929</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13174</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>13056</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>24458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,29%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18357</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>18544</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21106</t>
+          <t>21610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34049</t>
+          <t>33889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,6%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>14855</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>866</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13904,12 +13904,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31105</t>
+          <t>31619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42355</t>
+          <t>42674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45971</t>
+          <t>45570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54355</t>
+          <t>54332</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79691</t>
+          <t>80186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93974</t>
+          <t>94468</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17945</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12927</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14403,12 +14403,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>17787</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27504</t>
+          <t>27649</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18576</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27880</t>
+          <t>27265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39223</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53147</t>
+          <t>53296</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17452</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>13859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>14232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27854</t>
+          <t>27404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15386,7 +15386,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27395</t>
+          <t>27617</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25168</t>
+          <t>24784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35799</t>
+          <t>35379</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44899</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59718</t>
+          <t>59954</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18971</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>14440</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>30285</t>
+          <t>29057</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7667</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15767,12 +15767,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11543</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14551</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11942</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19558</t>
+          <t>19875</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>21104</t>
+          <t>21291</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32165</t>
+          <t>32438</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,48%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>13174</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11522</t>
+          <t>10885</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22336</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,07%</t>
         </is>
       </c>
     </row>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16524,7 +16524,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>24722</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>30105</t>
+          <t>30157</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,7 +16925,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>24705</t>
+          <t>23806</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>51842</t>
+          <t>51543</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>59485</t>
+          <t>59577</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>17123</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>29757</t>
+          <t>29746</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>27775</t>
+          <t>27649</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>40925</t>
+          <t>40759</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>47714</t>
+          <t>48794</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>66562</t>
+          <t>67806</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,8%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>35545</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>48760</t>
+          <t>48511</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>22471</t>
+          <t>22253</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>35748</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>62395</t>
+          <t>60612</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>81912</t>
+          <t>79871</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>61,02%</t>
         </is>
       </c>
     </row>
@@ -17803,7 +17803,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17888,7 +17888,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -17951,7 +17951,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>36463</t>
+          <t>36781</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>50909</t>
+          <t>51260</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>36473</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>51702</t>
+          <t>50575</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>77353</t>
+          <t>76956</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>97563</t>
+          <t>98278</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,34%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>25653</t>
+          <t>25173</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>40974</t>
+          <t>39603</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>21721</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>35308</t>
+          <t>35814</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>51191</t>
+          <t>50732</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>71651</t>
+          <t>70932</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>44,99%</t>
         </is>
       </c>
     </row>
@@ -18485,7 +18485,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18500,7 +18500,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18663,12 +18663,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18678,12 +18678,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18761,7 +18761,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18776,12 +18776,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>181633</t>
+          <t>183699</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>213641</t>
+          <t>212931</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>222138</t>
+          <t>219998</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>251939</t>
+          <t>252274</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>413795</t>
+          <t>414250</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>458273</t>
+          <t>457316</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,86%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>118909</t>
+          <t>120662</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>149764</t>
+          <t>149727</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>90285</t>
+          <t>89940</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>119371</t>
+          <t>119827</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>215620</t>
+          <t>217282</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>259512</t>
+          <t>260519</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>11508</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>25477</t>
+          <t>25907</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>19729</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>21542</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>39967</t>
+          <t>40805</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19330,7 +19330,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>14769</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19423,12 +19423,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>718</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
